--- a/salida/507100691_ACABADOS_TERRACOTA_SA_DE_CV/op_borrador.xlsx
+++ b/salida/507100691_ACABADOS_TERRACOTA_SA_DE_CV/op_borrador.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
   <si>
     <t>Plan tarifario</t>
   </si>
@@ -221,6 +221,9 @@
     <t>23 PONIENTE, 2905, BELIZARIO DOMINGUEZ, PUEBLA, PUEBLA, 72180</t>
   </si>
   <si>
+    <t>240729MKT0305</t>
+  </si>
+  <si>
     <t xml:space="preserve"> PLAN 799: REDES: WhatsApp (texto); Instagram; Facebook; Google Maps; Gmail;Uber,Waze    STREAMING: Youtube; Spotify; TikTok 2 GB</t>
   </si>
   <si>
@@ -231,6 +234,9 @@
   </si>
   <si>
     <t>APPLE IPHONE 18 PRO MAX 512GB 5G, GLACIAR</t>
+  </si>
+  <si>
+    <t>MPP</t>
   </si>
 </sst>
 </file>
@@ -570,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -699,15 +705,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -746,16 +743,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -776,6 +769,54 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2016,25 +2057,25 @@
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
       <c r="I8" s="25"/>
-      <c r="J8" s="60" t="s">
+      <c r="J8" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="59"/>
       <c r="M8" s="25"/>
-      <c r="N8" s="60" t="s">
+      <c r="N8" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="O8" s="61"/>
-      <c r="P8" s="61"/>
-      <c r="Q8" s="62"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="58"/>
+      <c r="Q8" s="59"/>
       <c r="R8" s="25"/>
-      <c r="S8" s="60" t="s">
+      <c r="S8" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="T8" s="61"/>
-      <c r="U8" s="61"/>
-      <c r="V8" s="62"/>
+      <c r="T8" s="58"/>
+      <c r="U8" s="58"/>
+      <c r="V8" s="59"/>
       <c r="W8" s="25"/>
       <c r="X8" s="38" t="s">
         <v>17</v>
@@ -2044,37 +2085,37 @@
     </row>
     <row r="9" spans="2:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="7"/>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
       <c r="I9" s="10"/>
-      <c r="J9" s="78">
+      <c r="J9" s="73">
         <v>507100691</v>
       </c>
-      <c r="K9" s="79"/>
-      <c r="L9" s="80"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="75"/>
       <c r="M9" s="10"/>
-      <c r="N9" s="75" t="s">
+      <c r="N9" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
-      <c r="Q9" s="77"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="72"/>
       <c r="R9" s="10"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="64"/>
-      <c r="U9" s="64"/>
-      <c r="V9" s="65"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="61"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="62"/>
       <c r="W9" s="10"/>
-      <c r="X9" s="81" t="s">
+      <c r="X9" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="Y9" s="81"/>
+      <c r="Y9" s="76"/>
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="2:26" ht="10" customHeight="1" x14ac:dyDescent="0.35">
@@ -2117,11 +2158,11 @@
       </c>
       <c r="H11" s="38"/>
       <c r="I11" s="25"/>
-      <c r="J11" s="60" t="s">
+      <c r="J11" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="61"/>
-      <c r="L11" s="62"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="59"/>
       <c r="M11" s="25"/>
       <c r="N11" s="38" t="s">
         <v>22</v>
@@ -2143,35 +2184,37 @@
     </row>
     <row r="12" spans="2:26" ht="24.65" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B12" s="7"/>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
+      <c r="G12" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="69"/>
       <c r="I12" s="8"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="65"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="62"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="74" t="s">
+      <c r="N12" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="74"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="81"/>
+      <c r="Q12" s="82"/>
       <c r="R12" s="8"/>
-      <c r="S12" s="55" t="s">
+      <c r="S12" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="57"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="84"/>
+      <c r="W12" s="84"/>
+      <c r="X12" s="84"/>
+      <c r="Y12" s="85"/>
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="2:26" ht="10" customHeight="1" x14ac:dyDescent="0.35">
@@ -2216,10 +2259,10 @@
       <c r="M14" s="20"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
@@ -2296,30 +2339,30 @@
       <c r="C16" s="27">
         <v>1</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="58">
+      <c r="E16" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="55">
         <v>24</v>
       </c>
-      <c r="G16" s="59"/>
-      <c r="H16" s="71" t="s">
-        <v>63</v>
-      </c>
-      <c r="I16" s="71"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="92"/>
       <c r="J16" s="27">
         <v>36999</v>
       </c>
       <c r="K16" s="26">
         <v>32859</v>
       </c>
-      <c r="L16" s="58">
+      <c r="L16" s="55">
         <v>24</v>
       </c>
-      <c r="M16" s="59"/>
+      <c r="M16" s="56"/>
       <c r="N16" s="26">
         <v>172.51</v>
       </c>
@@ -2339,7 +2382,9 @@
       <c r="T16" s="26">
         <v>2227054240</v>
       </c>
-      <c r="U16" s="28"/>
+      <c r="U16" s="28" t="s">
+        <v>65</v>
+      </c>
       <c r="V16" s="45" t="s">
         <v>52</v>
       </c>
@@ -2791,28 +2836,28 @@
     </row>
     <row r="33" spans="2:26" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
-      <c r="C33" s="67" t="s">
+      <c r="C33" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="68"/>
-      <c r="E33" s="69" t="s">
+      <c r="D33" s="65"/>
+      <c r="E33" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="69"/>
-      <c r="T33" s="70"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="66"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="66"/>
+      <c r="N33" s="66"/>
+      <c r="O33" s="66"/>
+      <c r="P33" s="66"/>
+      <c r="Q33" s="66"/>
+      <c r="R33" s="66"/>
+      <c r="S33" s="66"/>
+      <c r="T33" s="67"/>
       <c r="U33" s="17"/>
       <c r="V33" s="33" t="s">
         <v>48</v>
@@ -2859,26 +2904,26 @@
     </row>
     <row r="35" spans="2:26" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
-      <c r="C35" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="48"/>
+      <c r="C35" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="87"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="87"/>
+      <c r="N35" s="87"/>
+      <c r="O35" s="87"/>
+      <c r="P35" s="87"/>
+      <c r="Q35" s="87"/>
+      <c r="R35" s="87"/>
+      <c r="S35" s="87"/>
+      <c r="T35" s="88"/>
       <c r="U35" s="17"/>
       <c r="V35" s="31" t="s">
         <v>33</v>
